--- a/R_Codes/DataSummary/Archaea/Sample_Type/Archaea_Summary_Domain_by_Sample_Type.xlsx
+++ b/R_Codes/DataSummary/Archaea/Sample_Type/Archaea_Summary_Domain_by_Sample_Type.xlsx
@@ -384,10 +384,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>99.9999999999997</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>0.622953572773905</v>
+        <v>0.622880861117178</v>
       </c>
     </row>
   </sheetData>
@@ -426,7 +426,7 @@
         <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>1.5917387092895</v>
+        <v>1.59774664554867</v>
       </c>
     </row>
   </sheetData>
